--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487179_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487179_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0113</v>
+        <v>1.3966</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6076</v>
+        <v>2.207</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5963000000000001</v>
+        <v>-0.8104</v>
       </c>
       <c r="G2" t="n">
         <v>1.4561</v>
@@ -610,13 +610,13 @@
         <v>0.193</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3622</v>
+        <v>-0.2525</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3107</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0515</v>
+        <v>-0.1626</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6846</v>
+        <v>0.7382</v>
       </c>
       <c r="E3" t="n">
         <v>0.6029</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0818</v>
+        <v>0.1353</v>
       </c>
       <c r="G3" t="n">
         <v>0.7825</v>
@@ -688,13 +688,13 @@
         <v>0.193</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2908</v>
+        <v>-0.2373</v>
       </c>
       <c r="T3" t="n">
         <v>-0.0595</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2313</v>
+        <v>-0.1778</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. HERRERO CRESPO</t>
+          <t>P. FERNANDEZ MENDIGUCHIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.3869</v>
+        <v>-2.2508</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7137</v>
+        <v>-1.0182</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.1006</v>
+        <v>-1.2326</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.9129</v>
+        <v>-1.0108</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1849</v>
+        <v>-0.0569</v>
       </c>
       <c r="I4" t="n">
-        <v>-4.0978</v>
+        <v>-0.9539</v>
       </c>
       <c r="J4" t="n">
-        <v>1.311</v>
+        <v>0.1035</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5406</v>
+        <v>0.1035</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.2295</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.2239</v>
+        <v>-1.1143</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3557</v>
+        <v>-0.1604</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.8682</v>
+        <v>-0.9539</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.193</v>
+        <v>-0.772</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7371</v>
+        <v>0.193</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5512</v>
+        <v>-0.468</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2049</v>
+        <v>-0.1566</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7562</v>
+        <v>-0.3113</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2702</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1278</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8576</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ MENDIGUCHIA</t>
+          <t>M. HERRERO CRESPO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.5046</v>
+        <v>-2.4603</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.2185</v>
+        <v>1.3726</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2862</v>
+        <v>-3.8329</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0108</v>
+        <v>-2.9129</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0569</v>
+        <v>1.1849</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9539</v>
+        <v>-4.0978</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1035</v>
+        <v>1.311</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1035</v>
+        <v>2.5406</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-1.2295</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1143</v>
+        <v>-4.2239</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1604</v>
+        <v>-1.3557</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9539</v>
+        <v>-2.8682</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.772</v>
+        <v>-0.193</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R5" t="n">
-        <v>0.193</v>
+        <v>1.7371</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7218</v>
+        <v>-0.6246</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3569</v>
+        <v>-0.1361</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3649</v>
+        <v>-0.4885</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.2702</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.1278</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.8576</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.3173</v>
+        <v>-2.7839</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6793</v>
+        <v>-0.1191</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.638</v>
+        <v>-2.6648</v>
       </c>
       <c r="G6" t="n">
         <v>-3.3474</v>
@@ -922,13 +922,13 @@
         <v>1.9301</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2208</v>
+        <v>-0.6874</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1303</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0906</v>
+        <v>-0.1173</v>
       </c>
       <c r="V6" t="n">
         <v>0.2859</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.4006</v>
+        <v>-2.8136</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6235</v>
+        <v>2.1837</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.024</v>
+        <v>-4.9973</v>
       </c>
       <c r="G7" t="n">
         <v>-2.8149</v>
@@ -1000,13 +1000,13 @@
         <v>1.7371</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.9717</v>
+        <v>-1.3848</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2492</v>
+        <v>-0.6891</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7225</v>
+        <v>-0.6957</v>
       </c>
       <c r="V7" t="n">
         <v>0.614</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.9193</v>
+        <v>-4.9807</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.75</v>
+        <v>-0.4902</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.1693</v>
+        <v>-4.4905</v>
       </c>
       <c r="G8" t="n">
         <v>-3.7282</v>
@@ -1078,13 +1078,13 @@
         <v>0.579</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5843</v>
+        <v>-0.6458</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8923</v>
+        <v>-0.6325</v>
       </c>
       <c r="U8" t="n">
-        <v>0.308</v>
+        <v>-0.0132</v>
       </c>
       <c r="V8" t="n">
         <v>-1.1857</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.3136</v>
+        <v>-5.734</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1859</v>
+        <v>-1.6866</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.1277</v>
+        <v>-4.0474</v>
       </c>
       <c r="G9" t="n">
         <v>-4.7156</v>
@@ -1156,13 +1156,13 @@
         <v>1.3511</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2439</v>
+        <v>-0.1765</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3239</v>
+        <v>-0.1768</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.08</v>
+        <v>0.0003</v>
       </c>
       <c r="V9" t="n">
         <v>-1.228</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. DE LA CRUZ MARTINEZ</t>
+          <t>C. POLANCO MERINO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.4513</v>
+        <v>-6.2326</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0753</v>
+        <v>-2.0261</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.376</v>
+        <v>-4.2065</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.6237</v>
+        <v>-4.4627</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.1425</v>
+        <v>-2.8576</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.4812</v>
+        <v>-1.6051</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.98</v>
+        <v>-0.4587</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2795</v>
+        <v>-0.5072</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7004</v>
+        <v>0.0486</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.6437</v>
+        <v>-4.0041</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.8629</v>
+        <v>-2.3504</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.7808</v>
+        <v>-1.6537</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3511</v>
+        <v>1.158</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.579</v>
+        <v>1.158</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4766</v>
+        <v>-1.0437</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1652</v>
+        <v>-0.9111</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3113</v>
+        <v>-0.1325</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.8842</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. POLANCO MERINO</t>
+          <t>G. DE LA CRUZ MARTINEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.6331</v>
+        <v>-6.6179</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1857</v>
+        <v>-3.3757</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.4475</v>
+        <v>-3.2422</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.4627</v>
+        <v>-4.6237</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.8576</v>
+        <v>-2.1425</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.6051</v>
+        <v>-2.4812</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4587</v>
+        <v>-0.98</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5072</v>
+        <v>-0.2795</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0486</v>
+        <v>-0.7004</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.0041</v>
+        <v>-3.6437</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.3504</v>
+        <v>-1.8629</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.6537</v>
+        <v>-1.7808</v>
       </c>
       <c r="P11" t="n">
-        <v>1.158</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R11" t="n">
-        <v>1.158</v>
+        <v>0.579</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4442</v>
+        <v>-0.6431</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0708</v>
+        <v>-0.4656</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3735</v>
+        <v>-0.1775</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8842</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.808</v>
+        <v>-10.0024</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.9975</v>
+        <v>-5.8974</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.8105</v>
+        <v>-4.105</v>
       </c>
       <c r="G12" t="n">
         <v>-7.7906</v>
@@ -1390,13 +1390,13 @@
         <v>1.9301</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7013</v>
+        <v>-0.8956</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7601</v>
+        <v>-0.66</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0588</v>
+        <v>-0.2357</v>
       </c>
       <c r="V12" t="n">
         <v>0.614</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-42.0388</v>
+        <v>-41.7414</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.544499999999999</v>
+        <v>-8.2471</v>
       </c>
       <c r="F13" t="n">
         <v>-33.4943</v>
@@ -1468,13 +1468,13 @@
         <v>11.5805</v>
       </c>
       <c r="S13" t="n">
-        <v>-7.3566</v>
+        <v>-7.0593</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.844799999999999</v>
+        <v>-4.547300000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.512</v>
+        <v>-2.5118</v>
       </c>
       <c r="V13" t="n">
         <v>-1.5138</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.9666</v>
+        <v>8.998900000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>7.7916</v>
+        <v>6.6901</v>
       </c>
       <c r="F14" t="n">
-        <v>2.175</v>
+        <v>2.3089</v>
       </c>
       <c r="G14" t="n">
         <v>5.7732</v>
@@ -1546,13 +1546,13 @@
         <v>1.3511</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7219</v>
+        <v>0.7542</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6459</v>
+        <v>0.5443</v>
       </c>
       <c r="U14" t="n">
-        <v>0.076</v>
+        <v>0.2098</v>
       </c>
       <c r="V14" t="n">
         <v>2.0856</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.436400000000001</v>
+        <v>8.9976</v>
       </c>
       <c r="E15" t="n">
-        <v>9.494400000000001</v>
+        <v>9.895</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.058</v>
+        <v>-0.8974</v>
       </c>
       <c r="G15" t="n">
         <v>7.1942</v>
@@ -1624,13 +1624,13 @@
         <v>0.579</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2789</v>
+        <v>0.2822</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4164</v>
+        <v>-0.0159</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1375</v>
+        <v>0.2981</v>
       </c>
       <c r="V15" t="n">
         <v>0.9421</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.4603</v>
+        <v>5.6874</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0641</v>
+        <v>3.2644</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3963</v>
+        <v>2.423</v>
       </c>
       <c r="G16" t="n">
         <v>6.3801</v>
@@ -1702,13 +1702,13 @@
         <v>1.158</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1381</v>
+        <v>0.3652</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1639</v>
+        <v>0.0364</v>
       </c>
       <c r="U16" t="n">
-        <v>0.302</v>
+        <v>0.3288</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2859</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.4214</v>
+        <v>5.233</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5109</v>
+        <v>2.9115</v>
       </c>
       <c r="F17" t="n">
-        <v>2.9105</v>
+        <v>2.3215</v>
       </c>
       <c r="G17" t="n">
         <v>3.5185</v>
@@ -1780,13 +1780,13 @@
         <v>1.3511</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9029</v>
+        <v>0.7145</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4759</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3788</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="V17" t="n">
         <v>0.614</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. PEREZ BENITO</t>
+          <t>I. PEDROSA BELLES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.8872</v>
+        <v>3.0829</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6117</v>
+        <v>3.4055</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2755</v>
+        <v>-0.3226</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4001</v>
+        <v>2.3752</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5565</v>
+        <v>-1.1592</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1564</v>
+        <v>3.5344</v>
       </c>
       <c r="J18" t="n">
-        <v>2.1326</v>
+        <v>3.1094</v>
       </c>
       <c r="K18" t="n">
-        <v>2.0026</v>
+        <v>-0.1708</v>
       </c>
       <c r="L18" t="n">
-        <v>0.13</v>
+        <v>3.2802</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2675</v>
+        <v>-0.7341</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5538999999999999</v>
+        <v>-0.9883</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2863</v>
+        <v>0.2542</v>
       </c>
       <c r="P18" t="n">
-        <v>0.193</v>
+        <v>0.772</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.158</v>
+        <v>0.772</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2941</v>
+        <v>0.5496</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4442</v>
+        <v>0.2961</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1501</v>
+        <v>0.2535</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. PEDROSA BELLES</t>
+          <t>J. PEREZ BENITO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.5485</v>
+        <v>2.8277</v>
       </c>
       <c r="E19" t="n">
-        <v>3.005</v>
+        <v>1.3113</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4565</v>
+        <v>1.5164</v>
       </c>
       <c r="G19" t="n">
-        <v>2.3752</v>
+        <v>2.4001</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1592</v>
+        <v>2.5565</v>
       </c>
       <c r="I19" t="n">
-        <v>3.5344</v>
+        <v>-0.1564</v>
       </c>
       <c r="J19" t="n">
-        <v>3.1094</v>
+        <v>2.1326</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1708</v>
+        <v>2.0026</v>
       </c>
       <c r="L19" t="n">
-        <v>3.2802</v>
+        <v>0.13</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7341</v>
+        <v>0.2675</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9883</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2542</v>
+        <v>-0.2863</v>
       </c>
       <c r="P19" t="n">
-        <v>0.772</v>
+        <v>0.193</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R19" t="n">
-        <v>0.772</v>
+        <v>1.158</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0152</v>
+        <v>0.2346</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1044</v>
+        <v>0.1438</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1196</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. ERRASTI UGARTE</t>
+          <t>G. TSULAIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4878</v>
+        <v>2.6033</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1953</v>
+        <v>0.4011</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2925</v>
+        <v>2.2022</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9318</v>
+        <v>1.1574</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3799</v>
+        <v>-0.3321</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5518999999999999</v>
+        <v>1.4895</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7061</v>
+        <v>0.9767</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0143</v>
+        <v>-0.3985</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6919</v>
+        <v>1.3752</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7743</v>
+        <v>0.1806</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6344</v>
+        <v>0.0664</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.14</v>
+        <v>0.1142</v>
       </c>
       <c r="P20" t="n">
-        <v>0.579</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R20" t="n">
-        <v>0.579</v>
+        <v>1.5441</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9769</v>
+        <v>0.3834</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4891</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4878</v>
+        <v>0.4775</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>2.4137</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.4137</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. TSULAIA</t>
+          <t>M. ERRASTI UGARTE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.8082</v>
+        <v>2.1269</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.09959999999999999</v>
+        <v>1.995</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9078</v>
+        <v>0.1319</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1574</v>
+        <v>0.9318</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3321</v>
+        <v>0.3799</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4895</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9767</v>
+        <v>1.7061</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3985</v>
+        <v>1.0143</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3752</v>
+        <v>0.6919</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1806</v>
+        <v>-0.7743</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0664</v>
+        <v>-0.6344</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1142</v>
+        <v>-0.14</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3511</v>
+        <v>0.579</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5441</v>
+        <v>0.579</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4118</v>
+        <v>0.616</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5949</v>
+        <v>0.2889</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1831</v>
+        <v>0.3272</v>
       </c>
       <c r="V21" t="n">
-        <v>2.4137</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.4137</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.5827</v>
+        <v>1.436</v>
       </c>
       <c r="E22" t="n">
-        <v>2.7021</v>
+        <v>2.5019</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1194</v>
+        <v>-1.0659</v>
       </c>
       <c r="G22" t="n">
         <v>2.7839</v>
@@ -2170,13 +2170,13 @@
         <v>0.965</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9267</v>
+        <v>0.78</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5632</v>
+        <v>0.3629</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3635</v>
+        <v>0.4171</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1278</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B. MENDIA SANGRONIZ</t>
+          <t>I. CHACON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9586</v>
+        <v>0.5508</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.3016</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3946</v>
+        <v>0.2491</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5278</v>
+        <v>0.2348</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.9895</v>
+        <v>-1.4096</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5173</v>
+        <v>1.6444</v>
       </c>
       <c r="J23" t="n">
-        <v>1.3489</v>
+        <v>1.0488</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4863</v>
+        <v>-0.4813</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8625</v>
+        <v>1.5302</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.821</v>
+        <v>-0.8141</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4758</v>
+        <v>-0.9283</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.1142</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.772</v>
+        <v>-0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R23" t="n">
-        <v>1.158</v>
+        <v>0.965</v>
       </c>
       <c r="S23" t="n">
-        <v>2.1449</v>
+        <v>0.8877</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8593</v>
+        <v>0.2178</v>
       </c>
       <c r="U23" t="n">
-        <v>1.2856</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9421</v>
+        <v>-0.5717</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.228</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. PÉREZ DE SAN ROMÁN</t>
+          <t>B. MENDIA SANGRONIZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4577</v>
+        <v>0.3102</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8539</v>
+        <v>0.2635</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3961</v>
+        <v>0.0466</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1087</v>
+        <v>0.5278</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1087</v>
+        <v>-0.9895</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1.5173</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3053</v>
+        <v>1.3489</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3053</v>
+        <v>0.4863</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>0.8625</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.414</v>
+        <v>-0.821</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.414</v>
+        <v>-1.4758</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>-0.772</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.158</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5665</v>
+        <v>1.4965</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5486</v>
+        <v>0.5589</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0178</v>
+        <v>0.9376</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.9421</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>I. CHACON RODRIGUEZ</t>
+          <t>D. PÉREZ DE SAN ROMÁN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0233</v>
+        <v>0.1841</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1991</v>
+        <v>0.5535</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2224</v>
+        <v>-0.3694</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2348</v>
+        <v>-0.1087</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.4096</v>
+        <v>-0.1087</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6444</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1.0488</v>
+        <v>0.3053</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.4813</v>
+        <v>0.3053</v>
       </c>
       <c r="L25" t="n">
-        <v>1.5302</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.8141</v>
+        <v>-0.414</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.9283</v>
+        <v>-0.414</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1142</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.965</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3602</v>
+        <v>0.2928</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2829</v>
+        <v>0.2482</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6431</v>
+        <v>0.0446</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.5717</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.5717</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>42.03870000000001</v>
+        <v>42.03880000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>33.4943</v>
+        <v>33.49440000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>8.544599999999999</v>
+        <v>8.544300000000002</v>
       </c>
       <c r="G26" t="n">
         <v>33.1683</v>
@@ -2482,13 +2482,13 @@
         <v>11.5803</v>
       </c>
       <c r="S26" t="n">
-        <v>7.356699999999999</v>
+        <v>7.3567</v>
       </c>
       <c r="T26" t="n">
         <v>2.5119</v>
       </c>
       <c r="U26" t="n">
-        <v>4.8447</v>
+        <v>4.8448</v>
       </c>
       <c r="V26" t="n">
         <v>1.5139</v>
